--- a/CARTERA.xlsx
+++ b/CARTERA.xlsx
@@ -391,9 +391,6 @@
     <t>LU1883854355</t>
   </si>
   <si>
-    <t>LU0593848301</t>
-  </si>
-  <si>
     <t>LU0507266061</t>
   </si>
   <si>
@@ -428,6 +425,9 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>0P0000TXJZ</t>
   </si>
 </sst>
 </file>
@@ -447,14 +447,17 @@
       <i/>
       <sz val="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="7"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="6"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1058,7 +1061,7 @@
         <v>120</v>
       </c>
       <c r="G1" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1076,13 +1079,13 @@
         <v>6961.5</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1100,13 +1103,13 @@
         <v>2455</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>110</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1124,13 +1127,13 @@
         <v>5514.6</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>108</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1148,13 +1151,13 @@
         <v>2551</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>106</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1172,13 +1175,13 @@
         <v>947.8</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>104</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1196,13 +1199,13 @@
         <v>1342.8</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>102</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1220,13 +1223,13 @@
         <v>2351.21</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>100</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1244,13 +1247,13 @@
         <v>2995.91</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>98</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1268,13 +1271,13 @@
         <v>2083</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>96</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1291,13 +1294,13 @@
         <v>1192</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>94</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1314,13 +1317,13 @@
         <v>1318.78</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>92</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1338,13 +1341,13 @@
         <v>2130.56</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>90</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1361,13 +1364,13 @@
         <v>1508.88</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1384,13 +1387,13 @@
         <v>2242.67</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>86</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1408,13 +1411,13 @@
         <v>3353.15</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>84</v>
       </c>
       <c r="G16" s="21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1431,13 +1434,13 @@
         <v>1108.3900000000001</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>82</v>
       </c>
       <c r="G17" s="21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1455,13 +1458,13 @@
         <v>1490</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>80</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1479,13 +1482,13 @@
         <v>2467.5</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>78</v>
       </c>
       <c r="G19" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1503,13 +1506,13 @@
         <v>1552.5</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>76</v>
       </c>
       <c r="G20" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1527,13 +1530,13 @@
         <v>887.4</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>74</v>
       </c>
       <c r="G21" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1551,13 +1554,13 @@
         <v>1387.5</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>72</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1574,13 +1577,13 @@
         <v>1870.32</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>70</v>
       </c>
       <c r="G23" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1597,13 +1600,13 @@
         <v>2771.45</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>68</v>
       </c>
       <c r="G24" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1620,13 +1623,13 @@
         <v>1116.24</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1643,13 +1646,13 @@
         <v>1180.8</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>64</v>
       </c>
       <c r="G26" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1667,13 +1670,13 @@
         <v>2146.3200000000002</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>62</v>
       </c>
       <c r="G27" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1691,13 +1694,13 @@
         <v>2732.1</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>60</v>
       </c>
       <c r="G28" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1715,13 +1718,13 @@
         <v>2744</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>58</v>
       </c>
       <c r="G29" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1738,13 +1741,13 @@
         <v>1686.24</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>56</v>
       </c>
       <c r="G30" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1762,13 +1765,13 @@
         <v>804.75</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>54</v>
       </c>
       <c r="G31" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1786,13 +1789,13 @@
         <v>1060.5</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>52</v>
       </c>
       <c r="G32" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -1809,13 +1812,13 @@
         <v>738</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>50</v>
       </c>
       <c r="G33" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -1833,13 +1836,13 @@
         <v>3039.31</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>48</v>
       </c>
       <c r="G34" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -1856,13 +1859,13 @@
         <v>1215.26</v>
       </c>
       <c r="E35" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>46</v>
       </c>
       <c r="G35" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -1880,13 +1883,13 @@
         <v>1569.15</v>
       </c>
       <c r="E36" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>44</v>
       </c>
       <c r="G36" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -1903,13 +1906,13 @@
         <v>2160.75</v>
       </c>
       <c r="E37" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G37" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -1926,13 +1929,13 @@
         <v>1296.5899999999999</v>
       </c>
       <c r="E38" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>40</v>
       </c>
       <c r="G38" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -1950,13 +1953,13 @@
         <v>932.4</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>38</v>
       </c>
       <c r="G39" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -1974,13 +1977,13 @@
         <v>727.69999999999993</v>
       </c>
       <c r="E40" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G40" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -1998,13 +2001,13 @@
         <v>1768</v>
       </c>
       <c r="E41" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2022,13 +2025,13 @@
         <v>1124.0999999999999</v>
       </c>
       <c r="E42" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>32</v>
       </c>
       <c r="G42" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -2046,13 +2049,13 @@
         <v>1079.5999999999999</v>
       </c>
       <c r="E43" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>30</v>
       </c>
       <c r="G43" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -2069,13 +2072,13 @@
         <v>1109.77</v>
       </c>
       <c r="E44" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>28</v>
       </c>
       <c r="G44" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -2093,13 +2096,13 @@
         <v>994.80000000000007</v>
       </c>
       <c r="E45" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -2117,13 +2120,13 @@
         <v>1140.9000000000001</v>
       </c>
       <c r="E46" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>24</v>
       </c>
       <c r="G46" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -2140,13 +2143,13 @@
         <v>2643.32</v>
       </c>
       <c r="E47" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="G47" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -2164,13 +2167,13 @@
         <v>1325.1000000000001</v>
       </c>
       <c r="E48" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G48" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -2188,13 +2191,13 @@
         <v>886.9</v>
       </c>
       <c r="E49" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>18</v>
       </c>
       <c r="G49" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -2212,13 +2215,13 @@
         <v>1453</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G50" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -2236,13 +2239,13 @@
         <v>949.8</v>
       </c>
       <c r="E51" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G51" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -2259,13 +2262,13 @@
         <v>1189.92</v>
       </c>
       <c r="E52" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G52" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -2282,13 +2285,13 @@
         <v>1280.78</v>
       </c>
       <c r="E53" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G53" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -2305,13 +2308,13 @@
         <v>2247.65</v>
       </c>
       <c r="E54" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G54" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -2329,13 +2332,13 @@
         <v>2343.5</v>
       </c>
       <c r="E55" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G55" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -2353,13 +2356,13 @@
         <v>3147</v>
       </c>
       <c r="E56" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G56" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -2383,7 +2386,7 @@
         <v>117</v>
       </c>
       <c r="G57" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -2407,7 +2410,7 @@
         <v>119</v>
       </c>
       <c r="G58" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -2430,12 +2433,12 @@
         <v>118</v>
       </c>
       <c r="G59" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B60" s="7">
         <v>421.76</v>
@@ -2447,18 +2450,18 @@
         <v>5000</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F60" s="19" t="s">
         <v>123</v>
       </c>
       <c r="G60" s="21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B61" s="7">
         <v>26.3</v>
@@ -2470,18 +2473,18 @@
         <v>5000</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="G61" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B62" s="7">
         <v>163.80000000000001</v>
@@ -2493,18 +2496,18 @@
         <v>5000</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G62" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B63" s="7">
         <v>34.107999999999997</v>
@@ -2516,13 +2519,13 @@
         <v>5000</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G63" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
